--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -808,7 +808,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26.7% -&gt; 17.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>26.7% -&gt; 15.3% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -2556,111 +2556,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>70.17570645147902</v>
+        <v>103.9579534291615</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.5996246926746</v>
+        <v>116.5404104409828</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>80.23247283501188</v>
+        <v>134.9250535973918</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>87.70891982962939</v>
+        <v>164.5454667217586</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>98.20212182238502</v>
+        <v>220.698725084256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>61.61672294959897</v>
+        <v>87.6624525757782</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>64.65660196377915</v>
+        <v>95.7497920679405</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>68.39207774007043</v>
+        <v>106.800051725385</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>73.13394081045521</v>
+        <v>122.9278341935899</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>79.41052848198404</v>
+        <v>148.8880965042395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>54.67123187365499</v>
+        <v>75.36259663302229</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>56.77539111086816</v>
+        <v>80.75351613072056</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>62.34911976097469</v>
+        <v>97.32517470782793</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>66.22539660168512</v>
+        <v>111.2606663334557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>48.92547571168867</v>
+        <v>65.7551676969633</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>50.37817812821243</v>
+        <v>69.43185339144748</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>52.05983390850713</v>
+        <v>74.02908767939394</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>54.04926149567611</v>
+        <v>79.99204503129506</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>56.46614723712895</v>
+        <v>88.10811060392669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>44.09588838075481</v>
+        <v>58.047869408913</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>45.08446923626055</v>
+        <v>60.58637439004508</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>46.19544432508298</v>
+        <v>63.65776038482486</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>47.46661119207106</v>
+        <v>67.48395285635333</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>48.95311672978444</v>
+        <v>72.42997389688901</v>
       </c>
     </row>
     <row r="12">
@@ -2701,111 +2701,111 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.9%</t>
+          <t>terminal 13.3%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>85.12948232873711</v>
+        <v>142.9257201436457</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>82.63706811237466</v>
+        <v>138.8532208372788</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>80.23247283501188</v>
+        <v>134.9250535973918</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.91182515412919</v>
+        <v>131.1348279469485</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.67145970797428</v>
+        <v>127.4764945640268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.9%</t>
+          <t>terminal 14.3%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>72.61769026655179</v>
+        <v>113.2043612990502</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>70.46708294623669</v>
+        <v>109.9445769200784</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>68.39207774007043</v>
+        <v>106.800051725385</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>66.38934756098226</v>
+        <v>103.7656914075321</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>64.45574211341432</v>
+        <v>100.8366732530279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.9%</t>
+          <t>terminal 15.3%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>62.99176538945502</v>
+        <v>93.08744362839961</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>61.1040067005519</v>
+        <v>90.37756045690212</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>57.52421432810792</v>
+        <v>85.24035794052051</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>55.82651725053635</v>
+        <v>82.80482756291119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 18.9%</t>
+          <t>terminal 16.3%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>55.35999435733649</v>
+        <v>78.57430312065637</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>53.68052764295387</v>
+        <v>76.26098688087828</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>52.05983390850713</v>
+        <v>74.02908767939394</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>50.49533539472387</v>
+        <v>71.87501939979802</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>48.98459096491411</v>
+        <v>69.79538660824731</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 19.9%</t>
+          <t>terminal 17.3%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>49.16358515317348</v>
+        <v>67.61501378418899</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>47.65314483969517</v>
+        <v>65.60102680467182</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>46.19544432508298</v>
+        <v>63.65776038482486</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>44.78817430791364</v>
+        <v>61.78210484973862</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>43.42914772620249</v>
+        <v>59.97111565861656</v>
       </c>
     </row>
     <row r="20">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>87.9849315296462</v>
+        <v>92.11601318377691</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>76.79028280980998</v>
+        <v>90.6948601038554</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>61.89525166016686</v>
+        <v>88.2716081141819</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>59.27930478869805</v>
+        <v>87.76263937231083</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>56.82565682649614</v>
+        <v>87.25723444154944</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>59.28245930736963</v>
+        <v>87.76327116068845</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2892,19 +2892,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>31.94250897227312</v>
+        <v>50.91447338147828</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>45.61248413982136</v>
+        <v>69.33887227108335</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>72.95243447491782</v>
+        <v>106.1876700502934</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>86.62240964246601</v>
+        <v>124.6120689398984</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>59.2824593073696</v>
+        <v>87.76327116068842</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>59.2824593073696</v>
+        <v>87.76327116068842</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>59.28245930736963</v>
+        <v>87.76327116068845</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2944,19 +2944,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>67.45115350041955</v>
+        <v>97.52765330261191</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>62.86199945938025</v>
+        <v>92.04204535771109</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>58.57878902107689</v>
+        <v>86.92214460913688</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>53.68369137730164</v>
+        <v>81.07082946790932</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>49.09453733626231</v>
+        <v>75.58522152300843</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>45.13187476092197</v>
+        <v>66.47156186730963</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>56.25452670439153</v>
+        <v>83.04167945779123</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>67.31478474654207</v>
+        <v>99.51884490996628</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>73.36629892511395</v>
+        <v>108.5341680585322</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>78.49983059133066</v>
+        <v>116.1819146387544</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>54.67123187365499</v>
+        <v>75.36259663302229</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>56.77539111086816</v>
+        <v>80.75351613072056</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>59.28245930736959</v>
+        <v>87.7632711606884</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>62.34911976097469</v>
+        <v>97.32517470782793</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>66.22539660168512</v>
+        <v>111.2606663334557</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4015,14 +4015,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>21.60783306447023</v>
+        <v>28.78407997537623</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>96.98568399661953</v>
+        <v>133.7753850070414</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>21.60783306447023</v>
+        <v>28.78407997537623</v>
       </c>
     </row>
     <row r="7">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>96.98568399661953</v>
+        <v>133.7753850070414</v>
       </c>
     </row>
     <row r="8">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>26.7% → 17.9%</t>
+          <t>26.7% → 15.3%</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>67.84301903343683</v>
+        <v>81.67504702609115</v>
       </c>
     </row>
     <row r="19">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>67.29616575480996</v>
+        <v>93.77232461390484</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>31.35253335195464</v>
+        <v>33.87910174981675</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>50.02127247665867</v>
+        <v>64.15244367864858</v>
       </c>
     </row>
     <row r="25">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>59.36008732666913</v>
+        <v>89.33482995346847</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>50.00749186839327</v>
+        <v>66.64132982804048</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>67.84301903343683</v>
+        <v>81.67504702609115</v>
       </c>
     </row>
     <row r="26">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="C36" s="21" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="37">

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +148,7 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1004,23 +1005,23 @@
       <c r="D5" s="24" t="n">
         <v>35961.076614</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -1085,7 +1086,7 @@
       <c r="C9" s="24" t="n">
         <v>38180.002322</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1096,13 +1097,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="33" t="n">
         <v>151448.654828</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>249527.138687</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="33" t="n">
         <v>311099.090775</v>
       </c>
       <c r="E10" s="13" t="n"/>
@@ -1165,33 +1166,33 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="33" t="n">
         <v>35724.466132</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>55274.913356</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="33" t="n">
         <v>66870.86655000001</v>
       </c>
-      <c r="E14" s="32">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="F14" s="32">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="H14" s="32">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="I14" s="32">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
+      <c r="E14" s="33">
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$62)</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$62)</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$62)</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$62)</f>
+        <v/>
+      </c>
+      <c r="I14" s="33">
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$62)</f>
         <v/>
       </c>
     </row>
@@ -1226,23 +1227,23 @@
       <c r="D16" s="24" t="n">
         <v>55852.53459999998</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="32">
         <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -1253,34 +1254,34 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n">
+      <c r="B17" s="33" t="n">
         <v>16214.447271</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="33" t="n">
         <v>20902.939485</v>
       </c>
-      <c r="D17" s="32">
-        <f>Assumptions!$C$43</f>
-        <v/>
-      </c>
-      <c r="E17" s="32">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
-        <v/>
-      </c>
-      <c r="H17" s="32">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
-        <v/>
-      </c>
-      <c r="I17" s="32">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
+      <c r="D17" s="33">
+        <f>Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="33">
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="33">
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="33">
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$62*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -1290,35 +1291,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="38">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="38">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="38">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="38">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="38">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="38">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="38">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1329,15 +1330,15 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D10-(D11+D12+D13+D14+D15)</f>
         <v/>
       </c>
@@ -1479,7 +1480,7 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1494,7 +1495,7 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1509,7 +1510,7 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1524,12 +1525,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1561,12 +1562,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1631,12 +1632,12 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
@@ -1667,33 +1668,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -2052,17 +2053,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2133,38 +2134,38 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="D13" s="19">
-        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="E13" s="19">
-        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="F13" s="19">
-        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="G13" s="19">
-        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="H13" s="19">
-        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="I13" s="19">
-        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$45</f>
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -3473,35 +3474,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3512,36 +3513,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="38">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="38">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="38">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3788,12 +3789,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3810,12 +3811,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3832,12 +3833,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3854,12 +3855,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3883,7 +3884,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3894,7 +3895,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3905,7 +3906,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3916,7 +3917,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3927,7 +3928,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -4542,7 +4543,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>(1-Assumptions!$C$65)*(Assumptions!$C$62+Assumptions!$C$33*Assumptions!$C$63)+Assumptions!$C$65*Assumptions!$C$64*(1-Assumptions!$C$7)</f>
+        <f>(1-Assumptions!$C$78)*(Assumptions!$C$75+Assumptions!$C$33*Assumptions!$C$76)+Assumptions!$C$78*Assumptions!$C$77*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
@@ -4689,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5138,7 +5139,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Equity risk premium, TOTAL (split into the two legs below)</t>
         </is>
       </c>
       <c r="C32" s="21" t="n">
@@ -5200,7 +5201,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal equity risk premium, TOTAL</t>
         </is>
       </c>
       <c r="C37" s="21" t="n">
@@ -5240,7 +5241,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Balance-sheet and bridge anchors</t>
+          <t>The country premium, split — [R-COC-03]</t>
         </is>
       </c>
       <c r="B42" s="13" t="n"/>
@@ -5254,272 +5255,396 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>20560.003173</v>
+          <t>of which the MATURE equity premium — beta applies to this leg only</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>0.04242</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="n">
-        <v>6757.650507</v>
+          <t>Egypt country premium = sovereign default spread x 1.52</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>0.05168</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets and goodwill (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="n">
-        <v>1748.816945</v>
+          <t>Share of operations in Egypt (lambda)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>0.5928</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="n">
-        <v>19186.550057</v>
+          <t>Country premium on the operations outside Egypt</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0.0226</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="n">
-        <v>17330.24499</v>
+          <t>Country premium CHARGED — flat, once, never multiplied by beta</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>0.039838624</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FY2024 dividend per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
+          <t>Terminal mature equity premium</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>0.04242</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>1.85</v>
+          <t>Terminal Egypt country premium</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>0.02758000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
+          <t>Terminal country premium CHARGED — flat and once</t>
         </is>
       </c>
       <c r="C50" s="21" t="n">
-        <v>0.25</v>
+        <v>0.0212606279009288</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>0.1</v>
+          <t>Terminal beta — reverts to the market, not the measured beta</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="n">
-        <v>246</v>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
+      <c r="H53" s="13" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>20560.003173</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Terminal construction — the sanctioned one, never g x IC</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="n">
+        <v>6757.650507</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Terminal inflation (house Egyptian macro path)</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="n">
-        <v>0.07000000000000001</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>1748.816945</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="n">
-        <v>17.2627</v>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="n">
+        <v>19186.550057</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
         </is>
       </c>
       <c r="C58" s="24" t="n">
-        <v>126491.9551090501</v>
+        <v>17330.24499</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="n">
-        <v>0.1219271916645494</v>
+          <t>FY2024 dividend per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Currency-of-discounting alternative</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="13" t="n"/>
-      <c r="H61" s="13" t="n"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Days the dividend compounds — 4-Jun-2026 ex-date to the 3-Sep-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>US dollar risk-free rate</t>
+          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
         </is>
       </c>
       <c r="C62" s="21" t="n">
-        <v>0.043</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Hard-currency-leg equity risk premium</t>
+          <t>Growth in the share of equity-accounted investees</t>
         </is>
       </c>
       <c r="C63" s="21" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>US dollar cost of debt</t>
+          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
         </is>
       </c>
       <c r="C64" s="21" t="n">
-        <v>0.065</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Debt weight, USD leg</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Terminal growth of the USD leg</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="n">
-        <v>0.035</v>
-      </c>
+          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Terminal construction — the sanctioned one, never g x IC</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="n"/>
+      <c r="C67" s="13" t="n"/>
+      <c r="D67" s="13" t="n"/>
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="13" t="n"/>
+      <c r="H67" s="13" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="n"/>
-      <c r="C68" s="13" t="n"/>
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="13" t="n"/>
-      <c r="H68" s="13" t="n"/>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Terminal inflation (house Egyptian macro path)</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
+          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
         </is>
       </c>
       <c r="C69" s="28" t="n">
-        <v>6.5</v>
+        <v>17.2627</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="n">
-        <v>9</v>
+          <t>Terminal REAL growth — the stated one; nominal is derived, never supplied</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
+          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="n">
+        <v>126491.9551090501</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n">
+        <v>0.1219271916645494</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="13" t="n"/>
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="13" t="n"/>
+      <c r="G74" s="13" t="n"/>
+      <c r="H74" s="13" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>US dollar risk-free rate</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Hard-currency-leg equity risk premium</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>US dollar cost of debt</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="13" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n">
+      <c r="C84" s="21" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -5608,11 +5733,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5624,7 +5749,7 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>-Assumptions!$C$43</f>
+        <f>-Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D8" s="16">
@@ -5639,7 +5764,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="D9" s="16">
@@ -5653,7 +5778,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5668,7 +5793,7 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>-C10*$C$17</f>
         <v/>
       </c>
@@ -5683,11 +5808,11 @@
           <t>Less the employees' statutory share of profit</t>
         </is>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>-(C10+C11)*$C$18</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5699,11 +5824,11 @@
         </is>
       </c>
       <c r="B13" s="13" t="n"/>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>C13/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5726,7 +5851,7 @@
         </is>
       </c>
       <c r="C17" s="9">
-        <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
+        <f>(Assumptions!$C$57-Assumptions!$C$58)/Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -5737,7 +5862,7 @@
         </is>
       </c>
       <c r="C18" s="17">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -5937,7 +6062,7 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -5946,23 +6071,23 @@
         <v/>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="35">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="35">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="35">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -6071,23 +6196,23 @@
           <t>Group segment profit</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>SUM(F11:F13)</f>
         <v/>
       </c>
@@ -6157,23 +6282,23 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <f>B11-Assumptions!$B$22*E5</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>C11-Assumptions!$C$22*F5</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>D11-Assumptions!$D$22*G5</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>E11-Assumptions!$E$22*H5</f>
         <v/>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>F11-Assumptions!$F$22*I5</f>
         <v/>
       </c>
@@ -6184,23 +6309,23 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>B12-Assumptions!$B$22*E6</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C12-Assumptions!$C$22*F6</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D12-Assumptions!$D$22*G6</f>
         <v/>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <f>E12-Assumptions!$E$22*H6</f>
         <v/>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>F12-Assumptions!$F$22*I6</f>
         <v/>
       </c>
@@ -6211,23 +6336,23 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="32">
         <f>B13-Assumptions!$B$22*E7</f>
         <v/>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>C13-Assumptions!$C$22*F7</f>
         <v/>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="32">
         <f>D13-Assumptions!$D$22*G7</f>
         <v/>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>E13-Assumptions!$E$22*H7</f>
         <v/>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>F13-Assumptions!$F$22*I7</f>
         <v/>
       </c>
@@ -6238,23 +6363,23 @@
           <t>Group EBIT</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="35">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="35">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
@@ -6265,23 +6390,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>Assumptions!$C$27*E8</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>Assumptions!$C$27*F8</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>Assumptions!$C$27*G8</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>Assumptions!$C$27*H8</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
@@ -6292,23 +6417,23 @@
           <t>Group EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="35">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="35">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -6408,8 +6533,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="35">
-        <f>Assumptions!$C$69</f>
+      <c r="C6" s="36">
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -6419,7 +6544,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6430,7 +6555,7 @@
           <t>Discount factor back to the valuation date (year-2)</t>
         </is>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6452,7 +6577,7 @@
           <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C7*C8+C9</f>
         <v/>
       </c>
@@ -6464,8 +6589,8 @@
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
-      <c r="C11" s="33">
-        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+      <c r="C11" s="34">
+        <f>((C10-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
     </row>
@@ -6476,11 +6601,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((5.5*C5*C8+C9-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((8.0*C5*C8+C9-Assumptions!$C$54+Assumptions!$C$55)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
     </row>
@@ -6490,8 +6615,8 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="37">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
+      <c r="C13" s="38">
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$54)/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6501,7 +6626,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6512,7 +6637,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6523,8 +6648,8 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="37">
-        <f>Assumptions!$C$43/'Income Statement'!D7</f>
+      <c r="C16" s="38">
+        <f>Assumptions!$C$54/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6568,7 +6693,7 @@
           <t>Normalised EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6579,7 +6704,7 @@
           <t>Normalised EBIT (EGP mn)</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6612,7 +6737,7 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)</f>
         <v/>
       </c>
@@ -6634,8 +6759,8 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="37">
-        <f>Assumptions!$C$70</f>
+      <c r="C27" s="38">
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -6646,8 +6771,8 @@
         </is>
       </c>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="33">
-        <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
+      <c r="C28" s="34">
+        <f>C26*C27*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -6656,11 +6781,11 @@
         </is>
       </c>
       <c r="E28" s="16">
-        <f>C26*7*DCF!$C$61-Assumptions!$C$49</f>
+        <f>C26*7*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>C26*11.5*DCF!$C$61-Assumptions!$C$49</f>
+        <f>C26*11.5*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
     </row>
@@ -6694,7 +6819,7 @@
         </is>
       </c>
       <c r="C32" s="9">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
@@ -6726,7 +6851,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="38">
         <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
@@ -6738,8 +6863,8 @@
         </is>
       </c>
       <c r="B36" s="13" t="n"/>
-      <c r="C36" s="33">
-        <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
+      <c r="C36" s="34">
+        <f>C31*C35*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -6748,11 +6873,11 @@
         </is>
       </c>
       <c r="E36" s="16">
-        <f>((Assumptions!$C$71-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$84-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>((Assumptions!$C$71+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$84+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$60*(1+DCF!$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
     </row>
@@ -6916,23 +7041,23 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6943,23 +7068,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -6970,23 +7095,23 @@
           <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -6997,23 +7122,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>-F8</f>
         <v/>
       </c>
@@ -7024,23 +7149,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
@@ -7051,23 +7176,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -7078,23 +7203,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7105,23 +7230,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="39">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="39">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="39">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="39">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="39">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7132,23 +7257,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="40">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="40">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -7159,23 +7284,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -7193,7 +7318,7 @@
           <t>Terminal-year NOPAT — the LAST EXPLICIT year (FY2030), NOT grown (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>F10</f>
         <v/>
       </c>
@@ -7204,7 +7329,7 @@
           <t>Add back FY2030 book depreciation and amortisation (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>-F8</f>
         <v/>
       </c>
@@ -7215,7 +7340,7 @@
           <t>Terminal free cash flow to the firm — C20 + C21 less the capital charge on rows 65-67</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C20+C21+C65+C66+C67</f>
         <v/>
       </c>
@@ -7248,7 +7373,7 @@
           <t>Terminal value — C22 grown one year and capitalised at (C24 − C23) (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>C22*(1+C23)/(C24-C23)</f>
         <v/>
       </c>
@@ -7259,7 +7384,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7270,7 +7395,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7292,7 +7417,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7315,7 +7440,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n"/>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7356,7 +7481,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="39">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7367,7 +7492,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="41">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
@@ -7375,22 +7500,22 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Mature equity risk premium — beta applies to THIS leg and to nothing else</t>
         </is>
       </c>
       <c r="C38" s="23">
-        <f>Assumptions!$C$32</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity, explicit window</t>
-        </is>
-      </c>
-      <c r="C39" s="38">
-        <f>C36+C37*C38</f>
+          <t>Cost of equity, explicit window — country risk charged FLAT, once, beside beta not through it</t>
+        </is>
+      </c>
+      <c r="C39" s="39">
+        <f>C36+C37*C38+Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -7411,7 +7536,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="39">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7434,7 +7559,7 @@
         </is>
       </c>
       <c r="C43" s="19">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7444,7 +7569,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="39">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7455,7 +7580,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="39">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7467,7 +7592,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n"/>
-      <c r="C46" s="41">
+      <c r="C46" s="42">
         <f>C45*C39+C44*C41</f>
         <v/>
       </c>
@@ -7487,22 +7612,22 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal mature equity risk premium</t>
         </is>
       </c>
       <c r="C48" s="23">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
-        </is>
-      </c>
-      <c r="C49" s="38">
-        <f>C47+C37*C48</f>
+          <t>Terminal cost of equity — at a terminal beta of 1.00, not the measured beta</t>
+        </is>
+      </c>
+      <c r="C49" s="39">
+        <f>C47+Assumptions!$C$51*C48+Assumptions!$C$50</f>
         <v/>
       </c>
     </row>
@@ -7523,7 +7648,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="38">
+      <c r="C51" s="39">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7546,7 +7671,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n"/>
-      <c r="C53" s="41">
+      <c r="C53" s="42">
         <f>(1-C52)*C49+C52*C51</f>
         <v/>
       </c>
@@ -7617,23 +7742,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="38">
+      <c r="B57" s="39">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="39">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="38">
+      <c r="D57" s="39">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="38">
+      <c r="E57" s="39">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="38">
+      <c r="F57" s="39">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7658,8 +7783,8 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C61" s="39">
-        <f>(1+C39)^(Assumptions!$C$53/365)</f>
+      <c r="C61" s="40">
+        <f>(1+C39)^(Assumptions!$C$65/365)</f>
         <v/>
       </c>
     </row>
@@ -7670,8 +7795,8 @@
         </is>
       </c>
       <c r="B62" s="13" t="n"/>
-      <c r="C62" s="33">
-        <f>C31*C61-Assumptions!$C$49</f>
+      <c r="C62" s="34">
+        <f>C31*C61-Assumptions!$C$60*(1+$C$39)^(Assumptions!$C$61/365)</f>
         <v/>
       </c>
       <c r="D62" s="13" t="n"/>
@@ -7697,18 +7822,18 @@
         </is>
       </c>
       <c r="C65" s="19">
-        <f>F8*(1+Assumptions!$C$56)^(Assumptions!$C$57/2)</f>
+        <f>F8*(1+Assumptions!$C$68)^(Assumptions!$C$69/2)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Less capital for real growth — zero, because the stated real growth is zero</t>
-        </is>
-      </c>
-      <c r="C66" s="31">
-        <f>0</f>
+          <t>Less capital for real growth — the stated REAL growth times the FY2030 invested capital it has to buy</t>
+        </is>
+      </c>
+      <c r="C66" s="19">
+        <f>-Assumptions!$C$70*'Summary Financials'!I13</f>
         <v/>
       </c>
     </row>
@@ -7719,7 +7844,7 @@
         </is>
       </c>
       <c r="C67" s="19">
-        <f>-Assumptions!$C$58*Assumptions!$C$56</f>
+        <f>-Assumptions!$C$71*Assumptions!$C$68</f>
         <v/>
       </c>
     </row>
@@ -7834,32 +7959,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="33" t="n">
         <v>152186.247545</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="33" t="n">
         <v>231981.835577</v>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" s="33" t="n">
         <v>281049.081719</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="33">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="33">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="33">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="33">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7906,32 +8031,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="33" t="n">
         <v>20035.105205</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="33" t="n">
         <v>31601.46495</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="33" t="n">
         <v>28363.203246</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="33">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="33">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="33">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -8017,35 +8142,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="33">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="33">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="33">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -8065,24 +8190,24 @@
       <c r="D11" s="24" t="n">
         <v>-2145.438755</v>
       </c>
-      <c r="E11" s="31">
-        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="31">
-        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="31">
-        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="31">
-        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="31">
-        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+      <c r="E11" s="32">
+        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="32">
+        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="32">
+        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="32">
+        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="32">
+        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$64*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -8101,24 +8226,24 @@
       <c r="D12" s="24" t="n">
         <v>1568.902975</v>
       </c>
-      <c r="E12" s="31">
-        <f>D12*(1+Assumptions!$C$51)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31">
-        <f>E12*(1+Assumptions!$C$51)</f>
-        <v/>
-      </c>
-      <c r="G12" s="31">
-        <f>F12*(1+Assumptions!$C$51)</f>
-        <v/>
-      </c>
-      <c r="H12" s="31">
-        <f>G12*(1+Assumptions!$C$51)</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>H12*(1+Assumptions!$C$51)</f>
+      <c r="E12" s="32">
+        <f>D12*(1+Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>E12*(1+Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>F12*(1+Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>G12*(1+Assumptions!$C$63)</f>
+        <v/>
+      </c>
+      <c r="I12" s="32">
+        <f>H12*(1+Assumptions!$C$63)</f>
         <v/>
       </c>
     </row>
@@ -8128,35 +8253,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8176,23 +8301,23 @@
       <c r="D14" s="24" t="n">
         <v>-5591.139782</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8212,23 +8337,23 @@
       <c r="D15" s="24" t="n">
         <v>19186.550057</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8248,23 +8373,23 @@
       <c r="D16" s="24" t="n">
         <v>-1856.305067000001</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>-E15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>-F15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>-G15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>-H15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="32">
         <f>-I15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
@@ -8275,32 +8400,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n">
+      <c r="B17" s="33" t="n">
         <v>10115.701777</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="33" t="n">
         <v>17461.358714</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="33" t="n">
         <v>17330.24499</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="33">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="33">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="33">
         <f>I15+I16</f>
         <v/>
       </c>

--- a/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2561,19 +2561,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>103.9579534291615</v>
+        <v>104.0301624632969</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>116.5404104409828</v>
+        <v>116.6211865067517</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.0183472357894</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>164.5454667217586</v>
+        <v>164.6589280440988</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>220.698725084256</v>
+        <v>220.850419538668</v>
       </c>
     </row>
     <row r="7">
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>87.6624525757782</v>
+        <v>87.72356300452299</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>95.7497920679405</v>
+        <v>95.81640862987639</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>106.8741916763822</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>122.9278341935899</v>
+        <v>123.0129544822412</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>148.8880965042395</v>
+        <v>148.9908914140809</v>
       </c>
     </row>
     <row r="8">
@@ -2605,19 +2605,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.41532992422788</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.80991954166394</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.39286004781091</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.3378389089451</v>
       </c>
     </row>
     <row r="9">
@@ -2627,19 +2627,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>65.7551676969633</v>
+        <v>65.80135768206051</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>69.43185339144748</v>
+        <v>69.48054631668187</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.08091021732177</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>79.99204503129506</v>
+        <v>80.04792691139478</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>88.10811060392669</v>
+        <v>88.16951757590688</v>
       </c>
     </row>
     <row r="10">
@@ -2649,19 +2649,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>58.047869408913</v>
+        <v>58.08881027750758</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60.58637439004508</v>
+        <v>60.62904327864683</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.70252003806494</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>67.48395285635333</v>
+        <v>67.53131708874184</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>72.42997389688901</v>
+        <v>72.48070500205404</v>
       </c>
     </row>
     <row r="12">
@@ -2706,19 +2706,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>142.9257201436457</v>
+        <v>143.024503881775</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>138.8532208372788</v>
+        <v>138.9492096007453</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.0183472357894</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>131.1348279469485</v>
+        <v>131.2255218523266</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>127.4764945640268</v>
+        <v>127.5646799108681</v>
       </c>
     </row>
     <row r="15">
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>113.2043612990502</v>
+        <v>113.2828955946668</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>109.9445769200784</v>
+        <v>110.0208741777526</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>106.8741916763822</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>103.7656914075321</v>
+        <v>103.8377502299199</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>100.8366732530279</v>
+        <v>100.9067237627105</v>
       </c>
     </row>
     <row r="16">
@@ -2750,19 +2750,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>93.08744362839961</v>
+        <v>93.15227219205939</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>90.37756045690212</v>
+        <v>90.44052949139993</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>85.24035794052051</v>
+        <v>85.29980334431518</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>82.80482756291119</v>
+        <v>82.86260313979236</v>
       </c>
     </row>
     <row r="17">
@@ -2772,19 +2772,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>78.57430312065637</v>
+        <v>78.62924392140498</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>76.26098688087828</v>
+        <v>76.31434039371382</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.08091021732177</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>71.87501939979802</v>
+        <v>71.92536477488245</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>69.79538660824731</v>
+        <v>69.84430626571906</v>
       </c>
     </row>
     <row r="18">
@@ -2794,19 +2794,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>67.61501378418899</v>
+        <v>67.66248813099821</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>65.60102680467182</v>
+        <v>65.64711934901671</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.70252003806494</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>61.78210484973862</v>
+        <v>61.82557835469562</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>59.97111565861656</v>
+        <v>60.01334770570721</v>
       </c>
     </row>
     <row r="20">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.11601318377691</v>
+        <v>92.17996995001533</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>90.6948601038554</v>
+        <v>90.75790998185289</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>88.2716081141819</v>
+        <v>88.33310907770868</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>87.76263937231083</v>
+        <v>87.82381459630682</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>87.25723444154944</v>
+        <v>87.31808606401808</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2867,19 +2867,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>87.82444678911779</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2893,19 +2893,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>50.91447338147828</v>
+        <v>50.950588067254</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>69.33887227108335</v>
+        <v>69.38751742818589</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>106.1876700502934</v>
+        <v>106.2613761500496</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>124.6120689398984</v>
+        <v>124.6983055109813</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2919,19 +2919,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>87.82444678911776</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>87.82444678911776</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>87.82444678911777</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>97.52765330261191</v>
+        <v>97.59544299620889</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.04204535771109</v>
+        <v>92.10611928435993</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>86.92214460913688</v>
+        <v>86.98275048663422</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.07082946790932</v>
+        <v>81.12747186066198</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>75.58522152300843</v>
+        <v>75.63814814881297</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2971,19 +2971,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.47156186730963</v>
+        <v>66.51825425719441</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.04167945779123</v>
+        <v>83.09965272761718</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.51884490996628</v>
+        <v>99.58803577823238</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.5341680585322</v>
+        <v>108.6094965282676</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.1819146387544</v>
+        <v>116.2624496684627</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.41532992422788</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.80991954166394</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.39286004781091</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.3378389089451</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4016,14 +4016,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.80512018233149</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>133.8678939302773</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.80512018233149</v>
       </c>
     </row>
     <row r="7">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>133.8678939302773</v>
       </c>
     </row>
     <row r="8">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>81.73139139510033</v>
       </c>
     </row>
     <row r="19">
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>173.7120513766789</v>
+        <v>173.8288364577823</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>127.4805164686761</v>
+        <v>127.5665686336996</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>219.9435862846818</v>
+        <v>220.0911042818651</v>
       </c>
     </row>
     <row r="24">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>93.77232461390484</v>
+        <v>93.83596889146507</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>33.87910174981675</v>
+        <v>33.90293135551509</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.15244367864858</v>
+        <v>64.19639781793219</v>
       </c>
     </row>
     <row r="25">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>89.33482995346847</v>
+        <v>89.39708757884019</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>66.64132982804048</v>
+        <v>66.68784309439387</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>81.73139139510033</v>
       </c>
     </row>
     <row r="26">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>2140.777876</v>
+        <v>2139.355716</v>
       </c>
     </row>
     <row r="7">
